--- a/outputs/無駄の見える化_再現性で見る.xlsx
+++ b/outputs/無駄の見える化_再現性で見る.xlsx
@@ -90,7 +90,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -110,11 +110,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F7F7F7"/>
       </patternFill>
     </fill>
   </fills>
@@ -163,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -205,12 +200,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -846,7 +835,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="33" customHeight="1">
+    <row r="5" ht="46" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>①蓄積性</t>
@@ -859,21 +848,21 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>毎回ゼロからやり直す＝同じ労力を再投入（車輪の再発明）</t>
+          <t>毎回ゼロからやり直す＝同じ労力を再投入（作り直し）</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>仮説マップを新しい議事録・GPC実測が出るたびに作り直し。前回の検討が部品として残らないと毎回ゼロから。</t>
+          <t>DEG/MEG着色のメカニズム整理を、議論や分析結果が出るたびに大きく組み替え。前回の検討が部品として残らず毎回ゼロから。</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>1日に複数回の全面再構成。資料は更新されるが『何が確定し何が動いたか』の差分が積み上がらない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="33" customHeight="1">
+          <t>議論や新データのたびに整理を作り直し、『何が確定し何が動いたか』の差分が積み上がらない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>②非属人性</t>
@@ -891,12 +880,12 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>仮説の採否（残す/落とす）の判断基準が暗黙。基準が頭の中だと第三者は再判定できず、本人依存になる。</t>
+          <t>どの仮説を残す/落とすかの判断理由を書き残していない。頭の中だけだと他の人は同じ結論に辿り着けず、自分に聞きに来る。</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>高橋さんのSA仮説が本人の中に留まり共有されない＝属人化のリスク（個人でなく“共有の仕組みがない状態”）。</t>
+          <t>1次SA（高橋さん）で進む仮説検討の中身が本人に留まり、チームに回る流れがない＝属人化のリスク（“共有の仕組みがない状態”）。</t>
         </is>
       </c>
     </row>
@@ -918,12 +907,12 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>議事録・引き継ぎの反映が手作業で出所リンクなし。記述から元発言・元データに遡れないと再解釈でやり直し。</t>
+          <t>メカニズム整理や引き継ぎの反映で、どの記述がいつのどの議論・分析由来かを残していない。元に遡れず再解釈でやり直し。</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>リン酸添加位置のSIDE/TOP齟齬を抱えたまま配布物化。根拠が一意でないと受け手が判断できず差し戻る。</t>
+          <t>リン酸の添加位置（SIDE還流かTOP還流か）など記録が一意でない齟齬を抱えたまま資料化。根拠が一意でないと差し戻る。</t>
         </is>
       </c>
     </row>
@@ -945,12 +934,12 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>労力の方向（メカニズム検討）と組織優先（議事録に明記のSU対応優先）のズレ。深くても判断に接続しない。</t>
+          <t>自分が時間をかけるメカニズム整理が、組織が今優先するSU（立上げ）対応とズレると、深く詰めても判断に接続しない。</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>佐野デイリー会議／高橋SA仮説が回らず二重検討。TODO・最新版が一意でなく、誰も同じ前提に立てない。</t>
+          <t>日々の対策会議が分かれ、出られない回の濃い議論が共有遅れで初耳になる。最新版が一意でなく誰も同じ前提に立てない。</t>
         </is>
       </c>
     </row>
@@ -1010,7 +999,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="15" t="inlineStr">
         <is>
-          <t>無駄が出ている“状態”（症状）</t>
+          <t>どの業務で・何が起きているか（症状）</t>
         </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
@@ -1041,10 +1030,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="21" customHeight="1">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>仮説の採否基準が頭の中だけ → 新情報が来るたび全面作り直し</t>
+          <t>【メカニズム整理】議論や分析結果が出るたびに整理を大きく作り直し → 前回分が部品として残らず毎回ゼロから</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
@@ -1069,14 +1058,14 @@
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>採否ステータスと判定基準が記述に付き、差分追記で更新（作り直さない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="21" customHeight="1">
+          <t>仮説に『確定／検討中／棄却』のステータスと判定理由を付け、差分を追記して更新（作り直さない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>検討の出所（議事録・発言・データ）が記述に紐づかない → 元に遡れず再解釈で払い直し</t>
+          <t>【仮説の採否】どの仮説を残し・落としたかの理由を書き残さず → 後で『なぜ落としたか』を再検討してしまう</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
@@ -1086,157 +1075,157 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>採否の理由を一言ずつ書き残し、落とした案と理由が後から辿れる（撤回が“成果”として積み上がる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>【関係者との共有】1次SA（高橋さん）の仮説・分析結果が手元に回らず → 同じメカニズム検討を別々に進める</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>④②</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
           <t>大</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>仮説を“定量で詰める共通の場”に乗せ双方向で共有する（平尾＝接続役）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>【会議・議事録】日々の対策会議が分かれ、出られない回の濃い議論に後から追いつけない（共有遅れで初耳）</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>④①</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>★★☆</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>会議が判断の接続点として機能し、決定と根拠が一元で残り、欠席者も後から追える</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>【薬剤の効果整理】リン酸の添加位置（SIDE／TOP）など記録が一意でない齟齬を抱えたまま資料化</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>各記述に出所IDが紐づき、反映が追跡できる（content.py方式の横展開）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="21" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>没案と却下理由が残らない → 撤回済みの説を再び検討</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>③①</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>★★☆</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>条件・実績が一意に確定し、根拠付きで固定される</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>【仮説検討の議論】水分・各種アルデヒド・リン酸・CO2と可能性の羅列で物質収支が詰まらない（用語定義も未整合）</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>④＋定量</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>★★☆</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>落とした案と理由が残る。※鉄=触媒説を撤回できたのは根拠を残せたから＝好例の延長</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="21" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>高橋SA仮説が片務的で回らない → 同じメカニズム検討を二重に</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>④②</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>大</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>仮説が“定量で詰める共通の場”に乗り、双方向で共有される（平尾＝接続役）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="21" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>デイリー会議の分岐／最新版が一意でない → 誰も同じ前提に立てない</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>④①</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>★★☆</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>会議が判断の接続点として機能し、決定と根拠が一元で残る</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>【好例】資料生成はデータ(content.py)と表現(build/draw)を分離 → 1箇所直せば両成果物が自動再生成</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>横展</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>“二度払わない仕組み”の実証。必要な業務（採否管理・出所リンク・TODO一元化）に器として後から当てる</t>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>用語（ホルム／アセト等）の定義を揃え、定量で詰める論点に絞ってから議論する</t>
         </is>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>最初の1アクション：優先度★★★の中で容易性が高い一手から：仮説整理の『採否（残す/落とす）の判断基準』を1枚に言語化し、各記述に出所ID（議事録・発言・データ）を紐づける。content.py方式（データと表現の分離）を採否管理に横展開する。これで①蓄積性・③根拠性の二度払いが同時に止まり、効果を残業時間でモニタする。</t>
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>最初の1アクション：優先度★★★で着手しやすい一手から：メカニズム整理の『どの仮説を残し・落としたか』の判断理由を一言ずつ書き残し、各記述に“いつ・どの会議／分析が根拠か”を添える。これで①蓄積性（作り直し）と③根拠性（再検討の手戻り）の二度払いが同時に止まる。効果は『同じ整理を作り直す時間が減ったか』で確認する。</t>
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
@@ -1303,7 +1292,7 @@
       <c r="C4" s="6" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>再来</t>
         </is>
@@ -1313,14 +1302,14 @@
           <t>次に同じ状況が来たとき、この成果はそのまま再利用できるか？</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>Noなら→ 毎回ゼロから作り直し（①蓄積性の欠落）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>代替</t>
         </is>
@@ -1330,14 +1319,14 @@
           <t>自分以外の人が、これを使って同じ結論に到達できるか？</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Noなら→ 属人化・引き継ぎ不能（②非属人性）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>根拠</t>
         </is>
@@ -1347,14 +1336,14 @@
           <t>なぜその判断に至ったか（採否・解釈の根拠）が残っているか？</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>Noなら→ 検証で払い直す手戻り（③根拠性）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>接続</t>
         </is>
@@ -1364,7 +1353,7 @@
           <t>この成果は組織の判断や次工程に渡る形になっているか？</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Noなら→ 個人作業で死蔵・二重作業（④接続性）</t>
         </is>
@@ -1380,7 +1369,7 @@
       <c r="C9" s="6" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>没案</t>
         </is>
@@ -1390,26 +1379,26 @@
           <t>落とした案と落とした理由が残っているか？</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>Noなら→ 撤回済みの説を再検討する車輪の再発明</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>横展</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>この再現性の仕組み（例：content.py方式）を他業務へ展開できるか？</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>Noなら→ 好例が一箇所に閉じ改善が広がらない</t>
+          <t>ある業務で効いた“残し方・渡し方”を、他の業務にも展開できるか？</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>Noなら→ うまくいったやり方が一箇所に閉じ、改善が広がらない</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1412,7 @@
       <c r="C12" s="6" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>意図</t>
         </is>
@@ -1433,14 +1422,14 @@
           <t>この労力の方向は、組織が今優先していること（例：SU対応）と合っているか？</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>Noなら→ そもそも不要／空振り（第1階層：目的整合）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>定量</t>
         </is>
@@ -1450,7 +1439,7 @@
           <t>この論点は定量で詰められる状態か（定義が確定しているか）？</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Noなら→ 発散したまま結論が出ない議論（測定可能性）</t>
         </is>
@@ -1519,7 +1508,7 @@
       <c r="D4" s="6" t="n"/>
     </row>
     <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>【あるべき状態（ゴール像）】本人でなくても／時間が経っても同等以上の成果に最短到達でき、一度の労力が他者・未来の労力を肩代わりし、着手前に再現性を担保する“前さばき”が当たり前になっている運営。</t>
         </is>
@@ -1529,7 +1518,7 @@
       <c r="D5" s="6" t="n"/>
     </row>
     <row r="6" ht="23" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>STEP0 状態を定義する</t>
         </is>
@@ -1543,7 +1532,7 @@
       <c r="D6" s="6" t="n"/>
     </row>
     <row r="7" ht="23" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>STEP1 ギャップ＝病因を映す</t>
         </is>
@@ -1557,7 +1546,7 @@
       <c r="D7" s="6" t="n"/>
     </row>
     <row r="8" ht="23" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>STEP2 前さばきを設計に組み込む</t>
         </is>
@@ -1571,7 +1560,7 @@
       <c r="D8" s="6" t="n"/>
     </row>
     <row r="9" ht="23" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>STEP3 残業はモニタとして観測</t>
         </is>
@@ -1587,7 +1576,7 @@
     <row r="10" ht="53" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>【これは“器”：必要になってから作る】フォーマット・自動化・版管理ルールは、STEP0〜2で設計の方向が定まった後に初めて作る器（先に作ると打ち手先行）。種は手元にある＝横フロー資料の content.py（データ）をbuild/draw（表現）が読み、1箇所直せば両成果物が自動再生成される“データと表現の分離”。これを必要な業務（採否管理・出所リンク・TODO一元化）に後から当てるのが正しい順序。</t>
+          <t>【これは“器”：必要になってから作る】フォーマット・チェックリスト・記録の置き場所のルールは、STEP0〜2で方向が定まった後に作る器（先に作ると打ち手先行）。例：仮説の採否を理由付きで残す1枚／対策会議の決定事項を関係者が同じ場所で見られる置き方／変更条件（添加位置など）の記録を一意に固定する様式。いずれも目的は『担当や時間が変わっても、同じ結論に最短で戻れる』こと。</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
@@ -1615,7 +1604,7 @@
       <c r="D13" s="6" t="n"/>
     </row>
     <row r="14" ht="23" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>高橋さんのSA仮説の分断</t>
         </is>
@@ -1629,7 +1618,7 @@
       <c r="D14" s="6" t="n"/>
     </row>
     <row r="15" ht="23" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>佐野デイリー会議の分岐</t>
         </is>
@@ -1643,7 +1632,7 @@
       <c r="D15" s="6" t="n"/>
     </row>
     <row r="16" ht="23" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>属人化の扱い</t>
         </is>
@@ -1657,7 +1646,7 @@
       <c r="D16" s="6" t="n"/>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>平尾＝接続役（覚悟まで）</t>
         </is>
@@ -1701,7 +1690,7 @@
       <c r="D22" s="6" t="n"/>
     </row>
     <row r="23" ht="23" customHeight="1">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>案A（推奨）</t>
         </is>
@@ -1715,7 +1704,7 @@
       <c r="D23" s="6" t="n"/>
     </row>
     <row r="24" ht="23" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>案B（条件付き）</t>
         </is>
@@ -1729,7 +1718,7 @@
       <c r="D24" s="6" t="n"/>
     </row>
     <row r="25" ht="23" customHeight="1">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>提案</t>
         </is>

--- a/outputs/無駄の見える化_再現性で見る.xlsx
+++ b/outputs/無駄の見える化_再現性で見る.xlsx
@@ -158,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -187,6 +187,7 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -625,13 +626,13 @@
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
     </row>
-    <row r="6" ht="68" customHeight="1">
+    <row r="6" ht="83" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>無駄とは「やったこと」ではなく“状態”である。すなわち、かけた労力（時間・思考・調整・試行）がその場・その人の中だけで消費され、二度目・他者・次工程に渡らず“二度払い”になる状態。
+          <t>無駄とは「やったこと」ではなく“状態”である。すなわち、かけた労力（時間・思考・調整）が成果（人に説明できて・通って・使われるアウトプット）にならず、作り直し＝“二度払い”になる状態。
 問いを書き換える：×「どんな無駄があるか／どう減らすか」 → ○「どういう状態だと無駄につながるのか」。
-その答え＝仕事の再現性のなさ。再現性とは“労力を二度払わない仕組み”であり、再現性の欠如は単発の無駄ではなく『無駄を生み続ける装置』。
-主語を「私の労力」から「組織の総労力」へ上げる。一度の労力が他者・未来の労力まで肩代わりすれば“見合う成果”。同じ労力で同じ成果を出し続ける（毎回の作り直し）は、成果は出ていても再現性ゼロ＝無駄。</t>
+その答え＝仕事の再現性のなさ。「あの人だから／その時だからできた」のままだと、同じ労力をまた払う。
+私の業務に当てはめると、無駄はだいたい同じ形をしている＝『前提・目的・“動かない事実”・読み手を“握る”前に、先に作り込んでしまう』。だから後で説明できない／事実と矛盾／数字が差し替わる／目的とズレて、まるごと作り直しになる。（＝木村さんの「やる前に仮説と検証方針を共有してから動け、でないと無駄な作業になる」と同じこと。）</t>
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
@@ -786,14 +787,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>再現性の構成4要件</t>
+          <t>無駄になりやすい4つの軸</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>いずれの欠落も“二度払い”を生む。分類ではなく、再現性を成り立たせる要件。</t>
+          <t>どれかが欠けると作り直し（二度払い）になる。右は自分の業務での具体例。</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -811,142 +812,127 @@
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>要件</t>
+          <t>軸</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>一言でいうと</t>
+          <t>問い（一言）</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>欠落すると（どの二度払い）</t>
+          <t>欠けると（どの二度払い）</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>自分の業務での現れ（構造の層）</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>現場・朝会での現れ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>①蓄積性</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>一度の労力が次に部品として渡る</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>毎回ゼロからやり直す＝同じ労力を再投入（作り直し）</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>DEG/MEG着色のメカニズム整理を、議論や分析結果が出るたびに大きく組み替え。前回の検討が部品として残らず毎回ゼロから。</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>議論や新データのたびに整理を作り直し、『何が確定し何が動いたか』の差分が積み上がらない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>②非属人性</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>本人でなくても同じ結論へ到達できる</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>本人が抜けたら別の人がもう一度払う／聞きに行く待ちが発生</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>どの仮説を残す/落とすかの判断理由を書き残していない。頭の中だけだと他の人は同じ結論に辿り着けず、自分に聞きに来る。</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>1次SA（高橋さん）で進む仮説検討の中身が本人に留まり、チームに回る流れがない＝属人化のリスク（“共有の仕組みがない状態”）。</t>
-        </is>
-      </c>
+          <t>私の業務での具体例</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="n"/>
+    </row>
+    <row r="5" ht="33" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>①使い回せる</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>次に同じ状況が来たら、そのまま使えるか</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>使えない＝毎回ゼロから作り直し</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>アルデヒドのバランス計算を自己流で組み、標準指標や既存の解析例に揃っておらず、次に転用できず組み直し。</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>②自分以外でも分かる</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>本人でなくても同じ結論に辿り着けるか</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>無理＝属人。本人に聞かないと進まない</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>「自分が組める」計算と「人に説明できる」計算は別物。説明できる形になっておらず作り直しになった。</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
     </row>
     <row r="7" ht="33" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>③根拠性</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>なぜその判断に至ったかが残り検証できる</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>根拠を辿れず、検証や再判断でもう一度払う（手戻り）</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>メカニズム整理や引き継ぎの反映で、どの記述がいつのどの議論・分析由来かを残していない。元に遡れず再解釈でやり直し。</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>リン酸の添加位置（SIDE還流かTOP還流か）など記録が一意でない齟齬を抱えたまま資料化。根拠が一意でないと差し戻る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="33" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>④接続性</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>成果が次工程・組織の判断に渡る</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>個人作業で止まり、両側が別々に同じ労力を払う（二重作業）</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>自分が時間をかけるメカニズム整理が、組織が今優先するSU（立上げ）対応とズレると、深く詰めても判断に接続しない。</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>日々の対策会議が分かれ、出られない回の濃い議論が共有遅れで初耳になる。最新版が一意でなく誰も同じ前提に立てない。</t>
-        </is>
-      </c>
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>③根拠が残る</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>なぜその判断にしたか・裏取りが残っているか</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>残らない＝後で検証や差し替えの手戻り</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>P-1507のNPSHを図面実データを当たる前に概算値で『影響なし』と断定 → 実データで全面差し替え＋引き継ぎ書も修正。</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>④次に渡る／目的に合う</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>結果が読み手・目的・次工程に合う形か</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>合わない＝差し戻し・削り直し（二重作業）</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>温度計の新配置案が本来の目的（均一性監視）とズレ『6本でも36本でも同じ』と差し戻し。報告も伝える項目に絞れず削り直し。</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="7">
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="D5:E5"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="D4:E4"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -973,14 +959,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>無駄の見える化マップ</t>
+          <t>無駄の見える化マップ（自分の振り返り）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>主語は“業務”でなく“状態”。優先度＝規模×容易性で着手対象を絞る。</t>
+          <t>実際の業務で起きた“二度払い”。優先度＝規模×直しやすさで着手対象を絞る。</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -997,235 +983,215 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>どの業務で・何が起きているか（症状）</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>欠落要件</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>どの業務で・何が起きたか（自分の振り返り）</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>欠けた軸</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>規模
 労力×頻度</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>改善
-容易性</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>直し
+やすさ</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>あるべき状態</t>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>どこを“握れば”防げたか</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>【メカニズム整理】議論や分析結果が出るたびに整理を大きく作り直し → 前回分が部品として残らず毎回ゼロから</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>①②</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>【温度計削減】断線ケアでクーラント近傍にまとめた新配置案 → 目的（触媒層の均一性監視）とズレ『6本でも36本でも同じ』と差し戻し（手段の目的化・壁打ち前）</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>仮説に『確定／検討中／棄却』のステータスと判定理由を付け、差分を追記して更新（作り直さない）</t>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>着手前に『目的＝均一性監視』を握り、作り込む前に壁打ちで漏れを潰す</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>【仮説の採否】どの仮説を残し・落としたかの理由を書き残さず → 後で『なぜ落としたか』を再検討してしまう</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>③①</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>【着色メカニズム整理】教科書的に起こりそうな機構（鉄＋酸素ラジカル重合）から記述 → 『酸素雰囲気で色相悪化が止まる』動かない事実と真逆で大きく訂正</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>“動かない事実”を先に並べ、それと矛盾しない範囲に仮説を絞ってから書く</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>【P-1507 NPSH評価】図面・データシートを当たる前に概算値で『影響なし』と断定 → 実データ（NPSHa≈14m）で全面差し替え＋引き継ぎ書も修正</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>採否の理由を一言ずつ書き残し、落とした案と理由が後から辿れる（撤回が“成果”として積み上がる）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>【関係者との共有】1次SA（高橋さん）の仮説・分析結果が手元に回らず → 同じメカニズム検討を別々に進める</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>④②</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>大</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>数字を書く前に一次情報（図面・データシート）を当てる</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>【アルデヒドのバランス計算】標準指標／既存の解析例に揃えず自己流で組み → 人に説明できる形にならず組み直し</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>②①</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>仮説を“定量で詰める共通の場”に乗せ双方向で共有する（平尾＝接続役）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>【会議・議事録】日々の対策会議が分かれ、出られない回の濃い議論に後から追いつけない（共有遅れで初耳）</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>④①</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>★★☆</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>着手前に『一般的な指標・実例に揃える＝人に説明できる形』をゴールに置く</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>【報告・朝会の整理】伝える項目だけでよいのに作業細目や独自の言い回しを盛り → 後で削る二度手間</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>★★☆</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>会議が判断の接続点として機能し、決定と根拠が一元で残り、欠席者も後から追える</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>【薬剤の効果整理】リン酸の添加位置（SIDE／TOP）など記録が一意でない齟齬を抱えたまま資料化</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>★★☆</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>条件・実績が一意に確定し、根拠付きで固定される</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>【仮説検討の議論】水分・各種アルデヒド・リン酸・CO2と可能性の羅列で物質収支が詰まらない（用語定義も未整合）</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>④＋定量</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>★★☆</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>用語（ホルム／アセト等）の定義を揃え、定量で詰める論点に絞ってから議論する</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>最初の1アクション：優先度★★★で着手しやすい一手から：メカニズム整理の『どの仮説を残し・落としたか』の判断理由を一言ずつ書き残し、各記述に“いつ・どの会議／分析が根拠か”を添える。これで①蓄積性（作り直し）と③根拠性（再検討の手戻り）の二度払いが同時に止まる。効果は『同じ整理を作り直す時間が減ったか』で確認する。</t>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>書く前に『読み手＝その場で何を判断/共有したいか』に絞る</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="23" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>無駄の正体：共通点は『握り（目的・動かない事実・一次情報・読み手）を後回しにして、先に作り込む』こと。だからかけた労力が成果（説明できて・通って・使われる物）にならず、まるごと作り直しになる。</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="23" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>最初の一手：次に着手する検討・報告で、作り始める前に1行だけ書く：『目的／動かない事実／一次情報は当てたか／読み手』。それを壁打ちで当ててから作り込む。まず1件、これで作り直しが減るかを試す。</t>
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
@@ -1235,8 +1201,9 @@
       <c r="F12" s="6" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A12:F12"/>
   </mergeCells>
@@ -1251,7 +1218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1285,172 +1252,128 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>再現性4要件（この4つが診断の本体）</t>
+          <t>作り始める前に“握る”4つ（着手前チェック）</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>再来</t>
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>目的</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>次に同じ状況が来たとき、この成果はそのまま再利用できるか？</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>Noなら→ 毎回ゼロから作り直し（①蓄積性の欠落）</t>
+          <t>この作業の目的は何か。手段（データ取得・資料化）が目的化していないか？</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Noなら→ 目的とズレて差し戻し（④）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>代替</t>
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>動かない事実</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>自分以外の人が、これを使って同じ結論に到達できるか？</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>Noなら→ 属人化・引き継ぎ不能（②非属人性）</t>
+          <t>結論を縛る“動かない事実”を先に並べたか？</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Noなら→ 事実と矛盾して大訂正（③）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>根拠</t>
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>一次情報</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>なぜその判断に至ったか（採否・解釈の根拠）が残っているか？</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>Noなら→ 検証で払い直す手戻り（③根拠性）</t>
+          <t>数字・前提は一次情報（図面・データシート・実例）で裏取りしたか？</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Noなら→ 後で差し替え・引き継ぎ修正（③）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>接続</t>
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>読み手・ゴール</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>この成果は組織の判断や次工程に渡る形になっているか？</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>Noなら→ 個人作業で死蔵・二重作業（④接続性）</t>
+          <t>誰に渡すか／人に説明できる形になっているか？</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>Noなら→ 削り直し・組み直し（②④）</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>補強（4要件の応用）</t>
+          <t>出した後チェック</t>
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>没案</t>
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>壁打ち</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>落とした案と落とした理由が残っているか？</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>Noなら→ 撤回済みの説を再検討する車輪の再発明</t>
+          <t>作り込む“前”に、完成案を当てて漏れを潰す壁打ちを通したか？</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Noなら→ 壁打ち前に作り込み→作り直し</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>横展</t>
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>使い回し</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>ある業務で効いた“残し方・渡し方”を、他の業務にも展開できるか？</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>Noなら→ うまくいったやり方が一箇所に閉じ、改善が広がらない</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>別軸＝スコープ外の前提（再現性の前に仕分ける）</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>意図</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>この労力の方向は、組織が今優先していること（例：SU対応）と合っているか？</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>Noなら→ そもそも不要／空振り（第1階層：目的整合）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>定量</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>この論点は定量で詰められる状態か（定義が確定しているか）？</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>Noなら→ 発散したまま結論が出ない議論（測定可能性）</t>
+          <t>次に同じ状況が来たら、これはそのまま使えるか？</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>Noなら→ 毎回ゼロから（①）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A4:C4"/>
     <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A4:C4"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -1464,7 +1387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1507,10 +1430,10 @@
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
     </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>【あるべき状態（ゴール像）】本人でなくても／時間が経っても同等以上の成果に最短到達でき、一度の労力が他者・未来の労力を肩代わりし、着手前に再現性を担保する“前さばき”が当たり前になっている運営。</t>
+    <row r="5" ht="23" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>【ねらい】新しく様式やフォーマットを“作る”話ではない（それは打ち手先行）。作り直しの大半は『握る前に作り込む』から起きるので、着手の“順序”を変えるだけで防げる。</t>
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
@@ -1518,65 +1441,65 @@
       <c r="D5" s="6" t="n"/>
     </row>
     <row r="6" ht="23" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>STEP0 状態を定義する</t>
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>① まず握る（着手前）</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>「何を作るか」の前に、業務ごとに“再現性が確保された状態”を言語化して合意する。打ち手はその後。</t>
+          <t>作り始める前に1行で握る：『目的は何か／動かない事実は何か／一次情報は当てたか／誰に渡すか』。</t>
         </is>
       </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
     </row>
     <row r="7" ht="23" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>STEP1 ギャップ＝病因を映す</t>
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>② 壁打ちは作り込む前に</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>無駄リストでなく、4要件で“どの状態でどの要件が欠け二度払いになっているか”をマップ化（本資料§見える化マップ）。</t>
+          <t>木村さんの言う壁打ち（＝完成案を当てて漏れを潰す場）を、作り込んだ後でなく“前”に通す。相手は論点で選ぶ。</t>
         </is>
       </c>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
     </row>
     <row r="8" ht="23" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>STEP2 前さばきを設計に組み込む</t>
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>③ 戦う相手を選ぶ</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>着手前に『採否基準は何か／出所をどう残すか／誰に接続するか』を先に決める。事後の手戻りを構造的に消す。</t>
+          <t>勝ち筋の薄い検証（例：温度×DEG色相）に時間を奪われない。クリティカルパスから着手する。</t>
         </is>
       </c>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
     </row>
     <row r="9" ht="23" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>STEP3 残業はモニタとして観測</t>
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>④ 効果は作り直し量で見る</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>手戻り・車輪の再発明・待ち・分断が減れば、他条件一定なら残業は下がる。残業は目的でなく回復の観測値。</t>
+          <t>『同じ資料・計算を作り直した回数／時間が減ったか』で確認。残業削減は目的でなく結果。</t>
         </is>
       </c>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
     </row>
-    <row r="10" ht="53" customHeight="1">
+    <row r="10" ht="23" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>【これは“器”：必要になってから作る】フォーマット・チェックリスト・記録の置き場所のルールは、STEP0〜2で方向が定まった後に作る器（先に作ると打ち手先行）。例：仮説の採否を理由付きで残す1枚／対策会議の決定事項を関係者が同じ場所で見られる置き方／変更条件（添加位置など）の記録を一意に固定する様式。いずれも目的は『担当や時間が変わっても、同じ結論に最短で戻れる』こと。</t>
+          <t>様式・フォーマット・置き場所のルールは“器”で、上の順序が回り始めて必要になってから作れば足りる。先に器を作ると『ないものを作る』打ち手先行になり、本質（握る順序）が変わらない。</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
@@ -1593,10 +1516,10 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
     </row>
-    <row r="13" ht="38" customHeight="1">
+    <row r="13" ht="23" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>大前提：分断は『人の問題』でなく『再現性インフラの欠落』。個人を責めず、属人化を“リスク”として可視化する。撤回や齟齬は“誰がやってもこの状態なら起きる”と構造の層に置く（本人を低く見ることではない）。</t>
+          <t>他者を動かす話ではなく、自分の握り方の話。作り込む前に“当てる”相手を意図的に選ぶ。</t>
         </is>
       </c>
       <c r="B13" s="6" t="n"/>
@@ -1604,155 +1527,125 @@
       <c r="D13" s="6" t="n"/>
     </row>
     <row r="14" ht="23" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>高橋さんのSA仮説の分断</t>
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>壁打ち相手を論点で選ぶ</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>「共有しない人」でなく「共有が自然に起きる場がない状態」と捉える。平尾が“定量で詰める共通の場”を作り、片務を双方向に変える。</t>
+          <t>事業性→事業部／品質メカニズム→RD基礎研／EO系経験→藤本さん 等。完成案を当てて漏れを潰してから出す。</t>
         </is>
       </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
     </row>
     <row r="15" ht="23" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>佐野デイリー会議の分岐</t>
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>引き継ぎは“握り”ごと渡す</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>会議を「出席するもの」でなく「判断を接続し、決定と根拠を残す点」に再設計する触媒として動く。</t>
+          <t>結論だけでなく『目的・動かない事実・根拠（一次情報の出所）』を一緒に残す。本田尚之さんへのM50引き継ぎ等で徹底。</t>
         </is>
       </c>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
     </row>
     <row r="16" ht="23" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>属人化の扱い</t>
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>日次で早めに当てる</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>誰かを責めず、チェックで「ここが属人＝リスク」と事実として可視化し、判断基準を場に出すことを促す。</t>
+          <t>完成してから見せるのでなく、仮埋めの段階で日次共有し、ズレを小さいうちに直す（手戻りを最小化）。</t>
         </is>
       </c>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
     </row>
-    <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>平尾＝接続役（覚悟まで）</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>評論で終わらせない。構造問題と見抜いた人間が、その構造に最初に手を入れる。高橋仮説を定量議題に変換し、双方向共有・没案と根拠の保存を自分の作業と合意の両方で標準化する。</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>上位目的への接続（残業削減は結果指標）</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="38" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>握る前に作り込む“二度払い”を見える化　→　着手の順序を変える（握り→壁打ち→作る）　→　作り直し・差し戻し・削り直しが減る　→　（業務総量・要求水準が一定なら）残業削減 ＝結果であって目的でない　→　サステイナブルなキャリア形成 → 現場と組織への貢献</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
     </row>
-    <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>再現性欠落（二度払い）の見える化　→　再現性を高める設計を業務に組み込む（前さばきの文化）　→　同じ労力を二度払わない／属人化の解消　→　手戻り・車輪の再発明・待ち・分断が減る　→　（業務総量・要求水準が一定なら）残業削減 ＝結果指標であって目的でない　→　サステイナブルなキャリア形成　→　現場と組織への貢献（個人の検討が組織資産になり判断の質が上がる）</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>今日の発信スコープ案</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="38" customHeight="1">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>今日出す（推奨）</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>結論（無駄＝二度払い／本質＝再現性）→無駄の共通の形（握る前に作り込む）→自分の具体例3〜5件→順序の変え方。自分の実体験で語るので『打ち手先行』『きれい事』に聞こえない。</t>
+        </is>
+      </c>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
     </row>
     <row r="23" ht="23" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>案A（推奨）</t>
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>出し方の注意</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>§中心命題＋定義＋問いの書き換えを先に出し、『無駄＝再現性の欠如（二度払い）』という前提を関係者と合意。打ち手先行と誤読される余地が最小。</t>
+          <t>個人名（差し戻しの場面など）は伏せ『〜という指摘をもらった』と自分の振り返りとして話す。“ないものを作ろう”式の打ち手は出さない。</t>
         </is>
       </c>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
     </row>
-    <row r="24" ht="23" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>案B（条件付き）</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>見える化マップ以降まで一括。具体は伝わるが、合意前にマップを出すと『無駄リスト／打ち手先行』と読まれる余地。</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="23" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>まず案Aで土台を合意し、次回に見える化マップ・出口戦略・最初の1アクションを出す二段構え。</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="19">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="B14:D14"/>
-    <mergeCell ref="A22:D22"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="B17:D17"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B24:D24"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>

--- a/outputs/無駄の見える化_再現性で見る.xlsx
+++ b/outputs/無駄の見える化_再現性で見る.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="無駄の型" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="無駄の見える化" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,12 +68,6 @@
       <name val="IPAGothic"/>
       <color rgb="00000000"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="IPAGothic"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -144,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -172,15 +166,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -547,335 +532,237 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>業務効率化／無駄の見える化 ── 私の業務に見る“無駄の型”</t>
+          <t>業務効率化／無駄の見える化</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>無駄＝かけた労力が成果（説明できて・通って・使われる物）にならず、作り直し＝“二度払い”になる状態。原因は一つでなく型が複数ある。型を出して対策を広げる。</t>
+          <t>無駄＝かけた労力（努力）に対して見合わない成果になっている状態（木村さん 6/17）。見極める軸は“仕事の再現性”。自分ごとに落とすと「型・基盤がなく毎回ゼロから」になっている業務に無駄がある。</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>（2026-06-18 時点・木村さん 6/17発信への対応／自分の振り返り）</t>
+          <t>（2026-06-18・平尾）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>無駄とは何か（私の考え）</t>
+          <t>木村さんのお題（6/17 朝会）</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="53" customHeight="1">
+    </row>
+    <row r="5" ht="68" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>・無駄＝かけた労力が、成果（人に説明できて・通って・使われるアウトプット）にならず、作り直し＝“二度払い”になる状態。
-・その多くは「あの人だから／その時だからできた」で終わって次に活きない＝仕事の再現性のなさ。
-・ただし原因は一つではない。いろんな“型”がある。今日は型を洗い出して、対策をどんどん広げたい（1個直せば終わり、ではない）。</t>
+          <t>・業務効率化に向けて、「無駄と思われること・結果的に無駄になったこと」をまず見える化し、ピックアップして議論する。
+・最終的には残業削減を通じた“サステイナブルなキャリア形成”につなげたい。
+・無駄の定義（木村さん）＝「かけた努力（労力）に対して、見合わない成果になっている状態」。
+・木村さんの見方＝無駄につながるのは「仕事の再現性がないこと」。再現性のない取り組みは無駄になりやすい。</t>
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>無駄の型</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>カテゴリ</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>どういう状態が無駄か</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>私の実体験の例（複数PJ・過去〜直近）</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>対策の方向（行動・順序）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>① 発注・分担の切り分けすぎ</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>段取り・調達</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>本来一体の作業を別々の業者・部署に分けて発注し、責任の所在が曖昧になって品質問題と調整の手戻りが出る。</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>・2025年のEO触媒交換：充填と差圧測定を別々に発注し、責任分担が不備で品質問題の温床に。作業分担リストも未整備で「誰がどこまで」が曖昧だった。</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>受けた時点で「作業の境界＝誰がどこまで責任を持つか」を1枚に。本質的に一体の作業はセットで委託する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>② 手段の目的化</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>目的・ゴール設計</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>本来の目的を見失い、「データを取る」「ToDoを潰す」こと自体がゴールになる。</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>・温度計の新配置を断線対策でクラスタ配置したが、目的（触媒層の均一性監視）とズレ「6本でも36本でも同じ」と差し戻し。
-・異物対策で色相の原因究明に没入する一方、製品管理として当然付けるべきフィルターが付いていなかった（「色とは関係なく、必ず付けるべきものが付いていなかったのが問題」）。</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>着手前に「成功の状態＝何のためか」を一文で書く。施策案は「本来の目的が前進するか」を自問してから出す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>③ 勝ち筋の薄い検証に時間を奪われる</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>優先度・戦う相手</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>クリティカルパスでない・感度の弱い検証に没入し、本質的なタスクの時間を失う。</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>・EG品質で、温度×DEG色相の検証は感度が弱く「戦う相手でない／時間を無駄にするな」と整理。</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>着手前に「勝ち筋があるか／クリティカルパス上か」を判定。薄いものは優先度を下げ、難題（クリティカルパス）から着手する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="47" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>④ 壁打ち不足・レビュー未段取り</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>計画・進め方</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>自分／少人数で「できた」と思い、適切な相手の目を通さず出して差し戻し。レビュー時間も計画に入れず後手。</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>・配置案を計装と詰めただけで出し「壁打ち不足」と差し戻し→作り直し。
-・引継ぎ作業を相手に投げたまま止まり、催促が要る状態になった。</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>計画段階でレビュー期間と“壁打ち相手”を先に置く（相手は論点で選ぶ：事業性→事業部／メカニズム→基礎研／EO系→経験者）。完成案を持って当てる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>⑤ 作り込んでから方針転換</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>手戻り・試作</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>作り方・方式の見極めを早期にせず作り込み、後で「使えない」と判明して丸ごと作り直す。</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>・PFDの作成を何度も作り込んだが、必要な密度・正確性に届かず断念し方式を転換。
-・機器実績の整理も様式を固める前に作って全面作り直しになった。</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>本格着手の前に小さく試作して方式の妥当性（精度・安定性）を先に確認。ダメなら早く捨てる（仮埋めで芽を洗い出す）。</t>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>定義をもう少し開くと</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="53" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>・成果＝人に説明できて・通って・使われ、次に活きるアウトプット。
+・「見合わない成果」＝労力をかけたのに、使われない／毎回ゼロからやり直す／次に活きない状態（＝同じ労力を二度払う）。
+・だから無駄を見極める軸＝「再現性があるか」。“あの人だから・その時だからできた”では、同じ労力をまた払うことになる。</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>自分ごとに落とすと：再現性がない＝「型・基盤」がなく毎回ゼロから</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>領域</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>どういう状態が無駄か（型・基盤がない）</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>対策の方向（再現性を上げる）</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>⑥ 書き込みすぎ・不要情報の付加</t>
+          <t>報告書</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>アウトプット品質</t>
+          <t>毎回「構成・体裁をどうしよう」と考えるところに地味に時間がかかる。人によって作りもバラバラ。</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>相手・項目に絞れず、自分の作業細目・独自用語・前提を盛り込み、読み手の理解と自分の時間を浪費する。</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>・朝会向けの整理で、伝える項目だけでよいのに作業細目や独自の言い回しを盛り込み、「朝会で伝える内容じゃない、外して」と削り直し。</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>「相手が判断したいこと」を起点に結論と根拠だけにし、詳細は別紙へ。基準＝3分で結論と根拠が掴めるか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>強いて共通点を言えば（※1個直せば終わり、ではない）</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="23" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>強いて共通点を言えば、着手の前に「目的・前提（動かない事実／一次情報）・相手」を握れていないと作り直しになりやすい。ただし“1個直せば終わり”ではなく、上の型ごとに対策を打っていきたい。皆さんの「あるある」も足してほしい。</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-    </row>
-    <row r="17" ht="21" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>出し方</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>自分の振り返りとして話す。個人名や差し戻しの場面は伏せ「〜という指摘をもらった」と表現。</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="21" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>狙い</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>1個の原因に収束させず、種類の違う無駄を5〜6個出して、型ごとに対策を広げる議論の入口にする。</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="21" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>注意</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>「○○がない→作ろう」式の打ち手先行にしない。残業削減は目的でなく結果として見る。</t>
-        </is>
-      </c>
+          <t>考え方（目的→現状→課題→案→根拠→…→依頼）と体裁の型を共通で整備。毎回の判断をなくす。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>SA・変更管理</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>各段階で説明する相手（SA担当／部長／環境安全／製造現場）が違い、必要な説明も違う。毎回ゼロから組み立て、抜けも出る。</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>段階ごとに「ここでは誰に何を説明するか」を型に落として共通認識化。抜けなく速い。我々の業務で特にメリット大。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>企業検討会など各審査・検討会</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>審査・検討会ごとに、その都度どう説明するかを考え直している。</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>SAと同じ考え方で、段階・対象者ごとの説明の型に落とす。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>スケジュール</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>段階は規則で決まっているが、「実際に我々がここでこれをやる」という落とし込みが各自任せで、抜け漏れや後手が出る。</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>規則を“我々がやること”の共通認識（型）に落とす。これをやらなきゃね、が一目で分かる状態に。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="47" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>検討（データ解析）</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>各自がバラバラにデータを集めて解析している。同じことを別々に組み直し、属人化する。</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>①関係タグを集約した一式 ②それを引いて解析するツール（リンク紐付け） ③物性計算も周知の問題ないものを誰でもパッと——を共通化し、それを元にデータを組む。組織展開で加速。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>予算シート（マテバラ前提）</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>いろんな時期に作ったものを少しずつ改良して使っており、前提が実際の決算と乖離。見込み違いで後から手戻り（仕事を産む）が起きることがある。</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>切り詰めてしっかり検討できる基盤に整理する。前提と実績の突き合わせができる状態に。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>対策の方向（再現性を上げる）</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="53" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>・共通して言えるのは「誰でも抜けなくできる」状態にすること＝型・基盤を言語化して整備する（Excel等、形は何でもよい）。伝承だけでは続かない。
+・自分の中で閉じず、グループ・組織に展開すれば効きが加速する。
+・＝木村さんの言う再現性（“あの人だから・その時だからできた”を無くす）に直結する。残業削減はその結果。</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/outputs/無駄の見える化_再現性で見る.xlsx
+++ b/outputs/無駄の見える化_再現性で見る.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>無駄＝かけた労力（努力）に対して見合わない成果になっている状態（木村さん 6/17）。見極める軸は“仕事の再現性”。自分ごとに落とすと「型・基盤がなく毎回ゼロから」になっている業務に無駄がある。</t>
+          <t>無駄＝かけた労力（努力）に対して見合わない成果になっている状態（木村さん 6/17）。見極める軸は“仕事の再現性”。自分ごとに落とすと「進め方」と「仕組み（型・基盤）」の両方に無駄がある。</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -596,9 +596,9 @@
     <row r="8" ht="53" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>・成果＝人に説明できて・通って・使われ、次に活きるアウトプット。
-・「見合わない成果」＝労力をかけたのに、使われない／毎回ゼロからやり直す／次に活きない状態（＝同じ労力を二度払う）。
-・だから無駄を見極める軸＝「再現性があるか」。“あの人だから・その時だからできた”では、同じ労力をまた払うことになる。</t>
+          <t>・成果＝人に説明できて、使われて、次に活きるアウトプット。
+・「見合わない成果」＝労力をかけたのに、使われない／毎回ゼロからやり直す／次に活きない状態（＝同じ労力を“二度払い”）。
+・見極める軸＝「再現性があるか」。「あの人だからできた」「その時だからできた」で終わると、同じ労力をまた払うことになる。</t>
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
@@ -607,7 +607,7 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>自分ごとに落とすと：再現性がない＝「型・基盤」がなく毎回ゼロから</t>
+          <t>自分ごとに落とすと ①：進め方の無駄（どう動くか）</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
@@ -616,152 +616,183 @@
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>どういう状態が無駄か</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>例 ＋ 対策の方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="47" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>手段の目的化</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>本来の目的を見失い、「データを取る／ToDoを潰す」こと自体がゴールになる。</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>例：温度計を断線対策で増やす案が、目的（触媒層の均一性監視）とズレ「6本でも36本でも同じ」と差し戻し。色相究明に没入し、製品管理として当然付けるべきフィルターが抜けていたことも。
+→対策：着手前に「何のため＝成功の状態」を一文で書き、案は目的が前進するか自問してから出す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="47" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>勝ち筋の薄い検証に時間を奪われる</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>感度が弱い／クリティカルパス外の検証に没入し、本質的なタスクの時間を失う。</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>例：温度×DEG色相は感度が弱く「戦う相手でない／時間を無駄にするな」と整理。
+→対策：着手前に「勝ち筋があるか／クリティカルパス上か」を判定し、難題（クリティカルパス）から着手する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>自己完結で作り込んでから直す</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>壁打ち・確認・絞り込みを後回しにして作り込み、後で差し戻し・削り直しになる。</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>例：配置案を相手の目を通す前に出して「壁打ち不足」と差し戻し。確認しきる前に断定して書き、後で修正。
+→対策：完成案を“作り込む前”に壁打ち。レビュー期間を計画に入れ、結論と根拠に絞る（盛りすぎない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>自分ごとに落とすと ②：仕組み（型・基盤）の無駄（毎回ゼロから・属人）</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
           <t>領域</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>どういう状態が無駄か（型・基盤がない）</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>対策の方向（型・基盤を整備）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="47" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>検討の型（報告書・データ解析・物性・予算）</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>毎回ゼロから：報告書の構成を毎回考える／各自バラバラにデータを集めて解析を組み直す／予算シートは継ぎ接ぎ改良で実績と乖離し、見込み違いで手戻りが起きる。</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>検討〜まとめの型を共通化：①関係タグを集約した一式 ②それを引いて解析するツール（リンク紐付け） ③物性計算は“周知で問題ない”ものを誰でもパッと ④報告書の考え方・体裁の型 ⑤予算は前提と実績を突き合わせる基盤。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>SA・変更管理（審査）</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>各段階で相手（SA担当／部長／環境安全／製造現場）が違い、必要な説明も違う。毎回ゼロから組み立て、抜けも出る。</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>段階ごとに「ここでは誰に何を説明するか」を型に落として共通認識化。抜けなく速い（我々の業務で特にメリット大）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>スケジュール・ルール</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>段階は規則で決まっているが、企業検討会・申立てのスケジュールや「何をどこまでやるか」が各自任せで、抜け・後手が出る。</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>申立て・会議のスケジュールを頭に置き、「EG変更管理ではここまで通す」という明確なルール（共通認識）に落とす。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>対策の方向（再現性を上げる）</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>報告書</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>毎回「構成・体裁をどうしよう」と考えるところに地味に時間がかかる。人によって作りもバラバラ。</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>考え方（目的→現状→課題→案→根拠→…→依頼）と体裁の型を共通で整備。毎回の判断をなくす。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>SA・変更管理</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>各段階で説明する相手（SA担当／部長／環境安全／製造現場）が違い、必要な説明も違う。毎回ゼロから組み立て、抜けも出る。</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>段階ごとに「ここでは誰に何を説明するか」を型に落として共通認識化。抜けなく速い。我々の業務で特にメリット大。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>企業検討会など各審査・検討会</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>審査・検討会ごとに、その都度どう説明するかを考え直している。</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>SAと同じ考え方で、段階・対象者ごとの説明の型に落とす。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>スケジュール</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>段階は規則で決まっているが、「実際に我々がここでこれをやる」という落とし込みが各自任せで、抜け漏れや後手が出る。</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>規則を“我々がやること”の共通認識（型）に落とす。これをやらなきゃね、が一目で分かる状態に。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="47" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>検討（データ解析）</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>各自がバラバラにデータを集めて解析している。同じことを別々に組み直し、属人化する。</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>①関係タグを集約した一式 ②それを引いて解析するツール（リンク紐付け） ③物性計算も周知の問題ないものを誰でもパッと——を共通化し、それを元にデータを組む。組織展開で加速。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>予算シート（マテバラ前提）</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>いろんな時期に作ったものを少しずつ改良して使っており、前提が実際の決算と乖離。見込み違いで後から手戻り（仕事を産む）が起きることがある。</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>切り詰めてしっかり検討できる基盤に整理する。前提と実績の突き合わせができる状態に。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>対策の方向（再現性を上げる）</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="53" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>・共通して言えるのは「誰でも抜けなくできる」状態にすること＝型・基盤を言語化して整備する（Excel等、形は何でもよい）。伝承だけでは続かない。
-・自分の中で閉じず、グループ・組織に展開すれば効きが加速する。
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+    </row>
+    <row r="23" ht="68" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>・仕組み側＝型・基盤を言語化して整備する（Excel等、形は何でもよい）。伝承だけでは続かない。
+・進め方側＝着手前に「目的・勝ち筋・相手」を握り、作り込む前に壁打ちを通す。
+・どちらも自分の中で閉じず、グループ・組織に展開すれば効きが加速する。
 ・＝木村さんの言う再現性（“あの人だから・その時だからできた”を無くす）に直結する。残業削減はその結果。</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>

--- a/outputs/無駄の見える化_再現性で見る.xlsx
+++ b/outputs/無駄の見える化_再現性で見る.xlsx
@@ -593,12 +593,13 @@
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
     </row>
-    <row r="8" ht="53" customHeight="1">
+    <row r="8" ht="68" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>・成果＝人に説明できて、使われて、次に活きるアウトプット。
-・「見合わない成果」＝労力をかけたのに、使われない／毎回ゼロからやり直す／次に活きない状態（＝同じ労力を“二度払い”）。
-・見極める軸＝「再現性があるか」。「あの人だからできた」「その時だからできた」で終わると、同じ労力をまた払うことになる。</t>
+・「見合わない成果」＝労力をかけたのに、使われない／毎回ゼロからやり直す／次に活きない状態。
+・見極める軸＝「再現性があるか」。「あの人だからできた」「その時だからできた」で終わると、同じ仕事にまた労力がかかる。
+・つまり、再現性がないから手戻り（やり直し）が起きる——ここが無駄の正体。</t>
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
@@ -630,7 +631,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="47" customHeight="1">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>手段の目的化</t>
@@ -638,56 +639,56 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>本来の目的を見失い、「データを取る／ToDoを潰す」こと自体がゴールになる。</t>
+          <t>本来の目的を見失い、「データを取る／作業を片づける」こと自体がゴールになる。</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>例：温度計を断線対策で増やす案が、目的（触媒層の均一性監視）とズレ「6本でも36本でも同じ」と差し戻し。色相究明に没入し、製品管理として当然付けるべきフィルターが抜けていたことも。
-→対策：着手前に「何のため＝成功の状態」を一文で書き、案は目的が前進するか自問してから出す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="47" customHeight="1">
+          <t>例：温度計を断線対策で増やす案が、本来の目的（触媒層の均一性を見ること）とズレていて「6本でも36本でも同じ」と差し戻し。
+→対策：着手する前に「何のためか＝うまくいった状態」を一文で書き、案は『その目的が前に進むか』を確かめてから出す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>勝ち筋の薄い検証に時間を奪われる</t>
+          <t>勝ち筋の薄い検証に時間を取られる</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>感度が弱い／クリティカルパス外の検証に没入し、本質的なタスクの時間を失う。</t>
+          <t>効果が薄い・本筋でない検証に入り込み、本当にやるべきことの時間を失う。</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>例：温度×DEG色相は感度が弱く「戦う相手でない／時間を無駄にするな」と整理。
-→対策：着手前に「勝ち筋があるか／クリティカルパス上か」を判定し、難題（クリティカルパス）から着手する。</t>
+          <t>例：温度とDEG色相の関係を見る検証は効きが弱く「これは戦う相手ではない（時間を無駄にするな）」と整理した。
+→対策：着手する前に「勝ち目があるか／本筋（最優先）か」を見極め、難しい本筋から先に手をつける。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>自己完結で作り込んでから直す</t>
+          <t>自分の中だけで作り込んでから直す</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>壁打ち・確認・絞り込みを後回しにして作り込み、後で差し戻し・削り直しになる。</t>
+          <t>人に当てる・事実を確かめるのを後回しにして自分の中だけで作り込み、後で差し戻し・直しになる。</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>例：配置案を相手の目を通す前に出して「壁打ち不足」と差し戻し。確認しきる前に断定して書き、後で修正。
-→対策：完成案を“作り込む前”に壁打ち。レビュー期間を計画に入れ、結論と根拠に絞る（盛りすぎない）。</t>
+          <t>例：配置案を人の目を通す前に出して「壁打ち（人に当てて漏れを潰すこと）が足りない」と差し戻し。確かめきる前に言い切って書き、後で修正。
+→対策：完成イメージを“作り込む前”に人に当てる。直す時間も計画に入れ、中身は結論と根拠に絞る（盛りすぎない）。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>自分ごとに落とすと ②：仕組み（型・基盤）の無駄（毎回ゼロから・属人）</t>
+          <t>自分ごとに落とすと ②：仕組み（型・基盤）の無駄（毎回ゼロから・その人頼み）</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
@@ -773,10 +774,10 @@
     <row r="23" ht="68" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>・仕組み側＝型・基盤を言語化して整備する（Excel等、形は何でもよい）。伝承だけでは続かない。
-・進め方側＝着手前に「目的・勝ち筋・相手」を握り、作り込む前に壁打ちを通す。
-・どちらも自分の中で閉じず、グループ・組織に展開すれば効きが加速する。
-・＝木村さんの言う再現性（“あの人だから・その時だからできた”を無くす）に直結する。残業削減はその結果。</t>
+          <t>・仕組み側＝型・基盤を、誰でも使えるように書き出して整える（Excel等、形は何でもよい）。口頭の伝承だけでは続かない。
+・進め方側＝着手する前に「目的・勝ち目・相手」を先に決めて共有し、作り込む前に人に当てる。
+・どちらも自分の中だけに閉じず、グループ・組織に広げると効きが速くなる。
+・＝これが木村さんの言う再現性（“あの人だから・その時だからできた”を無くす）。残業が減るのはその結果。</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>

--- a/outputs/無駄の見える化_再現性で見る.xlsx
+++ b/outputs/無駄の見える化_再現性で見る.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -634,145 +634,127 @@
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>手段の目的化</t>
+          <t>勝ち筋の薄い検証に時間を取られる</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>本来の目的を見失い、「データを取る／作業を片づける」こと自体がゴールになる。</t>
+          <t>効果が薄い・本筋でない検証に入り込み、本当にやるべきことの時間を失う。</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>例：温度計を断線対策で増やす案が、本来の目的（触媒層の均一性を見ること）とズレていて「6本でも36本でも同じ」と差し戻し。
-→対策：着手する前に「何のためか＝うまくいった状態」を一文で書き、案は『その目的が前に進むか』を確かめてから出す。</t>
+          <t>例：温度とDEG色相の関係を見る検証は効きが弱く「これは戦う相手ではない（時間を無駄にするな）」と整理した。
+→対策：着手する前に「勝ち目があるか／本筋（最優先）か」を見極め、難しい本筋から先に手をつける。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>勝ち筋の薄い検証に時間を取られる</t>
+          <t>自分の中だけで作り込んでから直す</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>効果が薄い・本筋でない検証に入り込み、本当にやるべきことの時間を失う。</t>
+          <t>人に当てる・事実を確かめるのを後回しにして自分の中だけで作り込み、後で差し戻し・直しになる。</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>例：温度とDEG色相の関係を見る検証は効きが弱く「これは戦う相手ではない（時間を無駄にするな）」と整理した。
-→対策：着手する前に「勝ち目があるか／本筋（最優先）か」を見極め、難しい本筋から先に手をつける。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>自分の中だけで作り込んでから直す</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>人に当てる・事実を確かめるのを後回しにして自分の中だけで作り込み、後で差し戻し・直しになる。</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>例：配置案を人の目を通す前に出して「壁打ち（人に当てて漏れを潰すこと）が足りない」と差し戻し。確かめきる前に言い切って書き、後で修正。
+          <t>例：配置案を人の目を通す前に出して「人に当てて漏れを潰すことが足りない」と差し戻し。確かめきる前に言い切って書き、後で修正。
 →対策：完成イメージを“作り込む前”に人に当てる。直す時間も計画に入れ、中身は結論と根拠に絞る（盛りすぎない）。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>自分ごとに落とすと ②：仕組み（型・基盤）の無駄（毎回ゼロから・その人頼み）</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>領域</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>どういう状態が無駄か（型・基盤がない）</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>対策の方向（型・基盤を整備）</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="47" customHeight="1">
+    <row r="17" ht="47" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>検討の型（報告書・データ解析・物性・予算）</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>毎回ゼロから：報告書の構成を毎回考える／各自バラバラにデータを集めて解析を組み直す／予算シートは継ぎ接ぎ改良で実績と乖離し、見込み違いで手戻りが起きる。</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>検討〜まとめの型を共通化：①関係タグを集約した一式 ②それを引いて解析するツール（リンク紐付け） ③物性計算は“周知で問題ない”ものを誰でもパッと ④報告書の考え方・体裁の型 ⑤予算は前提と実績を突き合わせる基盤。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>検討の型（報告書・データ解析・物性・予算）</t>
+          <t>SA・変更管理（審査）</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>毎回ゼロから：報告書の構成を毎回考える／各自バラバラにデータを集めて解析を組み直す／予算シートは継ぎ接ぎ改良で実績と乖離し、見込み違いで手戻りが起きる。</t>
+          <t>各段階で相手（SA担当／部長／環境安全／製造現場）が違い、必要な説明も違う。毎回ゼロから組み立て、抜けも出る。</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>検討〜まとめの型を共通化：①関係タグを集約した一式 ②それを引いて解析するツール（リンク紐付け） ③物性計算は“周知で問題ない”ものを誰でもパッと ④報告書の考え方・体裁の型 ⑤予算は前提と実績を突き合わせる基盤。</t>
+          <t>段階ごとに「ここでは誰に何を説明するか」を型に落として共通認識化。抜けなく速い（我々の業務で特にメリット大）。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>SA・変更管理（審査）</t>
+          <t>スケジュール・ルール</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>各段階で相手（SA担当／部長／環境安全／製造現場）が違い、必要な説明も違う。毎回ゼロから組み立て、抜けも出る。</t>
+          <t>段階は規則で決まっているが、企業検討会・申立てのスケジュールや「何をどこまでやるか」が各自任せで、抜け・後手が出る。</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>段階ごとに「ここでは誰に何を説明するか」を型に落として共通認識化。抜けなく速い（我々の業務で特にメリット大）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>スケジュール・ルール</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>段階は規則で決まっているが、企業検討会・申立てのスケジュールや「何をどこまでやるか」が各自任せで、抜け・後手が出る。</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
           <t>申立て・会議のスケジュールを頭に置き、「EG変更管理ではここまで通す」という明確なルール（共通認識）に落とす。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>対策の方向（再現性を上げる）</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="68" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="68" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>・仕組み側＝型・基盤を、誰でも使えるように書き出して整える（Excel等、形は何でもよい）。口頭の伝承だけでは続かない。
 ・進め方側＝着手する前に「目的・勝ち目・相手」を先に決めて共有し、作り込む前に人に当てる。
@@ -780,19 +762,19 @@
 ・＝これが木村さんの言う再現性（“あの人だから・その時だからできた”を無くす）。残業が減るのはその結果。</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
